--- a/docs/downloads/04/tbl_cm_chars_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_chars_alaotra_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -397,12 +397,6 @@
           <t>Femme</t>
         </is>
       </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>6.5</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1171,12 +1165,6 @@
           <t>Divorcé(e)</t>
         </is>
       </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-      <c r="E38">
-        <v>3.2</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1194,12 +1182,6 @@
           <t>En concubinage</t>
         </is>
       </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-      <c r="E39">
-        <v>3.2</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1214,7 +1196,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D40">
@@ -1263,12 +1245,6 @@
           <t>Veuf(ve)</t>
         </is>
       </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
-      <c r="E42">
-        <v>3.2</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1286,12 +1262,6 @@
           <t>Célibataire</t>
         </is>
       </c>
-      <c r="D43">
-        <v>1</v>
-      </c>
-      <c r="E43">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1332,12 +1302,6 @@
           <t>En concubinage</t>
         </is>
       </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-      <c r="E45">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1352,7 +1316,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D46">
@@ -1447,12 +1411,6 @@
           <t>En concubinage</t>
         </is>
       </c>
-      <c r="D50">
-        <v>2</v>
-      </c>
-      <c r="E50">
-        <v>3.4</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1467,7 +1425,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D51">
@@ -1559,7 +1517,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D55">
@@ -1654,12 +1612,6 @@
           <t>En concubinage</t>
         </is>
       </c>
-      <c r="D59">
-        <v>1</v>
-      </c>
-      <c r="E59">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1674,7 +1626,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D60">
@@ -1746,12 +1698,6 @@
           <t>Célibataire</t>
         </is>
       </c>
-      <c r="D63">
-        <v>4</v>
-      </c>
-      <c r="E63">
-        <v>4.4</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1792,12 +1738,6 @@
           <t>En concubinage</t>
         </is>
       </c>
-      <c r="D65">
-        <v>4</v>
-      </c>
-      <c r="E65">
-        <v>4.4</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1812,14 +1752,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D66">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E66">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="67">
@@ -1835,14 +1775,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Marié(e) religieusement</t>
+          <t>Marié(e) selon la tradition</t>
         </is>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="E67">
-        <v>5.6</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="68">
@@ -1858,20 +1798,20 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Marié(e) selon la tradition</t>
+          <t>Veuf(ve)</t>
         </is>
       </c>
       <c r="D68">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E68">
-        <v>48.9</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1881,14 +1821,8 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Veuf(ve)</t>
-        </is>
-      </c>
-      <c r="D69">
-        <v>13</v>
-      </c>
-      <c r="E69">
-        <v>14.4</v>
+          <t>Célibataire</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -1904,14 +1838,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Célibataire</t>
+          <t>Divorcé(e)</t>
         </is>
       </c>
       <c r="D70">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E70">
-        <v>4.5</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="71">
@@ -1927,14 +1861,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Divorcé(e)</t>
+          <t>En concubinage</t>
         </is>
       </c>
       <c r="D71">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E71">
-        <v>12.4</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="72">
@@ -1950,14 +1884,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>En concubinage</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D72">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E72">
-        <v>10.1</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="73">
@@ -1973,14 +1907,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) selon la tradition</t>
         </is>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="E73">
-        <v>3.4</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="74">
@@ -1996,20 +1930,20 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Marié(e) religieusement</t>
+          <t>Veuf(ve)</t>
         </is>
       </c>
       <c r="D74">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E74">
-        <v>7.9</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2019,20 +1953,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Marié(e) selon la tradition</t>
-        </is>
-      </c>
-      <c r="D75">
-        <v>50</v>
-      </c>
-      <c r="E75">
-        <v>56.2</v>
+          <t>Célibataire</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2042,14 +1970,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Veuf(ve)</t>
+          <t>Divorcé(e)</t>
         </is>
       </c>
       <c r="D76">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E76">
-        <v>5.6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77">
@@ -2065,14 +1993,8 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Célibataire</t>
-        </is>
-      </c>
-      <c r="D77">
-        <v>2</v>
-      </c>
-      <c r="E77">
-        <v>2.7</v>
+          <t>En concubinage</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -2088,14 +2010,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Divorcé(e)</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D78">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E78">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -2111,14 +2033,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>En concubinage</t>
+          <t>Marié(e) selon la tradition</t>
         </is>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="E79">
-        <v>1.4</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="80">
@@ -2134,20 +2056,20 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Veuf(ve)</t>
         </is>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E80">
-        <v>2.7</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2157,20 +2079,20 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Marié(e) religieusement</t>
+          <t>Célibataire</t>
         </is>
       </c>
       <c r="D81">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E81">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2180,20 +2102,20 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Marié(e) selon la tradition</t>
+          <t>Divorcé(e)</t>
         </is>
       </c>
       <c r="D82">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E82">
-        <v>60.3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2203,14 +2125,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Veuf(ve)</t>
+          <t>En concubinage</t>
         </is>
       </c>
       <c r="D83">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E83">
-        <v>16.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="84">
@@ -2226,14 +2148,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Célibataire</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D84">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="E84">
-        <v>2.2</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="85">
@@ -2249,14 +2171,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Divorcé(e)</t>
+          <t>Marié(e) selon la tradition</t>
         </is>
       </c>
       <c r="D85">
-        <v>56</v>
+        <v>251</v>
       </c>
       <c r="E85">
-        <v>11</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="86">
@@ -2272,105 +2194,13 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>En concubinage</t>
+          <t>Veuf(ve)</t>
         </is>
       </c>
       <c r="D86">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="E86">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Statut matrimonial</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Marié(e) civilement</t>
-        </is>
-      </c>
-      <c r="D87">
-        <v>90</v>
-      </c>
-      <c r="E87">
-        <v>17.8</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Statut matrimonial</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Marié(e) religieusement</t>
-        </is>
-      </c>
-      <c r="D88">
-        <v>16</v>
-      </c>
-      <c r="E88">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Statut matrimonial</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Marié(e) selon la tradition</t>
-        </is>
-      </c>
-      <c r="D89">
-        <v>251</v>
-      </c>
-      <c r="E89">
-        <v>49.5</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Statut matrimonial</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Veuf(ve)</t>
-        </is>
-      </c>
-      <c r="D90">
-        <v>64</v>
-      </c>
-      <c r="E90">
         <v>12.6</v>
       </c>
     </row>

--- a/docs/downloads/04/tbl_cm_chars_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_chars_alaotra_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -401,7 +401,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -424,7 +424,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -447,7 +447,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -470,7 +470,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -516,7 +516,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -562,7 +562,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -654,7 +654,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -723,7 +723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -746,7 +746,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -769,7 +769,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -792,7 +792,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -812,7 +812,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -832,7 +832,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -852,7 +852,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -892,7 +892,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -952,7 +952,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -972,7 +972,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -992,7 +992,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1012,7 +1012,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1032,7 +1032,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1052,7 +1052,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1072,7 +1072,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1092,7 +1092,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1112,7 +1112,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1132,7 +1132,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1152,7 +1152,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1169,7 +1169,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1232,7 +1232,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1249,7 +1249,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1266,7 +1266,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1289,7 +1289,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1329,7 +1329,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1352,7 +1352,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1375,7 +1375,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1438,7 +1438,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1461,7 +1461,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1484,7 +1484,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1507,7 +1507,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1553,7 +1553,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1639,7 +1639,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1662,7 +1662,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1685,7 +1685,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1725,7 +1725,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1742,7 +1742,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1765,7 +1765,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1828,7 +1828,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1851,7 +1851,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1920,7 +1920,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1943,7 +1943,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1983,7 +1983,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2000,7 +2000,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2023,7 +2023,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2069,7 +2069,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2092,7 +2092,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2115,7 +2115,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2138,7 +2138,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2184,7 +2184,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
